--- a/saucedemo-login-tests.xlsx
+++ b/saucedemo-login-tests.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Plan de Test" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Bugs" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Panier" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="75">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -193,6 +194,100 @@
   <si>
     <t xml:space="preserve">Moyenne</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ét</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">apes</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TC06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter un produit au panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se connecter avec standard_user / secret_sauce → sur la page produits, cliquer sur "Add to cart" pour un produit (ex : Sauce Labs Backpack) → observer le bouton et l'icône panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">le bouton devient "Remove", l'icône du panier en haut à droite affiche "1"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">article ajouté au panier, panier affiche numéro « 1 »,  bouton article « ajouter » devient « remove »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter plusieurs produits au panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depuis la page produits, cliquer sur "Add to cart" pour 3 produits différents → observer l'icône panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">l'icône du panier affiche "3", et chaque bouton cliqué est passé sur "Remove" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">articles ajoutés au panier, panier affiche numéro « 3 »,  bouton articles « ajouter » deviennent « remove »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retirer un produit depuis la page produits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avec au moins 1 produit déjà ajouté, cliquer sur le bouton "Remove" du produit ajouté → observer le bouton et l'icône panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">le bouton redevient "Add to cart", le compteur du panier diminue de 1 (ou disparaît si c'était le seul produit) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">article retiré au panier, compteur panier diminue de « 1 » et disparaît bien si tous les articles enlevés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifier le contenu du panier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajouter 2 produits différents depuis la page produits → cliquer sur l'icône du panier en haut à droite → observer la page panier (Your Cart) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">les 2 produits ajoutés apparaissent avec le bon nom et le bon prix, correspondant à ce qui était affiché sur la page produits </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les 2 articles ajoutés apparaissent bien dans la page panier, avec les bons prix affichés sur la page produit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panier vide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans ajouter aucun produit (ou après avoir tout retiré), cliquer sur l'icône du panier → observer la page panier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">la page panier s'affiche normalement, sans produit listé, sans message d'erreur ni comportement anormal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">panier vide sans article, pas de produits listés, pas de message d’erreur, page panier affichée correctement</t>
+  </si>
 </sst>
 </file>
 
@@ -201,7 +296,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -233,6 +328,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -276,7 +377,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -286,6 +387,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -584,4 +689,149 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="88.18"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="81.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="46.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="69.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="58.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;A</oddHeader>
+    <oddFooter>&amp;CPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>